--- a/public/templates/Dental_CBCT_Test_Data_Template_NoTimer.xlsx
+++ b/public/templates/Dental_CBCT_Test_Data_Template_NoTimer.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L37"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -528,351 +528,367 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>mAs Range</v>
+        <v>Tolerance Operator</v>
       </c>
       <c r="B14" t="str">
-        <v>Measured mR 1</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Measured mR 2</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Measured mR 3</v>
-      </c>
-      <c r="E14" t="str">
-        <v>Average</v>
-      </c>
-      <c r="F14" t="str">
-        <v>mR/mAs</v>
+        <v>&lt;=</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>50</v>
+        <v>Tolerance Value (CoL)</v>
       </c>
       <c r="B15" t="str">
-        <v>12.2</v>
-      </c>
-      <c r="C15" t="str">
-        <v>12.25</v>
-      </c>
-      <c r="D15" t="str">
-        <v>12.22</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
+        <v>0.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>100</v>
+        <v>mAs Range</v>
       </c>
       <c r="B16" t="str">
-        <v>24.4</v>
+        <v>Measured mR 1</v>
       </c>
       <c r="C16" t="str">
-        <v>24.45</v>
+        <v>Measured mR 2</v>
       </c>
       <c r="D16" t="str">
-        <v>24.42</v>
+        <v>Measured mR 3</v>
       </c>
       <c r="E16" t="str">
-        <v/>
+        <v>Average</v>
       </c>
       <c r="F16" t="str">
+        <v>mR/mAs</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>50</v>
+      </c>
+      <c r="B17" t="str">
+        <v>12.2</v>
+      </c>
+      <c r="C17" t="str">
+        <v>12.25</v>
+      </c>
+      <c r="D17" t="str">
+        <v>12.22</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>TEST: CONSISTENCY OF RADIATION OUTPUT</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Tolerance Operator</v>
-      </c>
-      <c r="B19" t="str">
-        <v>&lt;=</v>
+        <v>100</v>
+      </c>
+      <c r="B18" t="str">
+        <v>24.4</v>
+      </c>
+      <c r="C18" t="str">
+        <v>24.45</v>
+      </c>
+      <c r="D18" t="str">
+        <v>24.42</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Tolerance Value (CoV)</v>
-      </c>
-      <c r="B20" t="str">
-        <v>0.05</v>
+        <v>TEST: CONSISTENCY OF RADIATION OUTPUT</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>FFD</v>
+        <v>Tolerance Operator</v>
       </c>
       <c r="B21" t="str">
-        <v>100</v>
+        <v>&lt;=</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>kVp</v>
+        <v>Tolerance Value (CoV)</v>
       </c>
       <c r="B22" t="str">
-        <v>mAs</v>
-      </c>
-      <c r="C22" t="str">
-        <v>Meas 1</v>
-      </c>
-      <c r="D22" t="str">
-        <v>Meas 2</v>
-      </c>
-      <c r="E22" t="str">
-        <v>Meas 3</v>
-      </c>
-      <c r="F22" t="str">
-        <v>Mean</v>
-      </c>
-      <c r="G22" t="str">
-        <v>CoV</v>
-      </c>
-      <c r="H22" t="str">
-        <v>Remarks</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>80</v>
+        <v>FFD</v>
       </c>
       <c r="B23" t="str">
         <v>100</v>
       </c>
-      <c r="C23" t="str">
-        <v>10.2</v>
-      </c>
-      <c r="D23" t="str">
-        <v>10.1</v>
-      </c>
-      <c r="E23" t="str">
-        <v>10.3</v>
-      </c>
-      <c r="F23" t="str">
-        <v/>
-      </c>
-      <c r="G23" t="str">
-        <v/>
-      </c>
-      <c r="H23" t="str">
-        <v/>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>kVp</v>
+      </c>
+      <c r="B24" t="str">
+        <v>mAs</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Meas 1</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Meas 2</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Meas 3</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Mean</v>
+      </c>
+      <c r="G24" t="str">
+        <v>CoV</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Remarks</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>TEST: RADIATION LEAKAGE LEVEL FROM X-RAY TUBE HOUSE</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>kV</v>
-      </c>
-      <c r="B26" t="str">
-        <v>120</v>
-      </c>
-      <c r="C26" t="str">
-        <v>mA</v>
-      </c>
-      <c r="D26" t="str">
-        <v>10</v>
-      </c>
-      <c r="E26" t="str">
-        <v>Time</v>
-      </c>
-      <c r="F26" t="str">
-        <v>1.0</v>
-      </c>
-      <c r="G26" t="str">
-        <v>Workload</v>
-      </c>
-      <c r="H26" t="str">
+        <v>80</v>
+      </c>
+      <c r="B25" t="str">
         <v>100</v>
       </c>
-      <c r="I26" t="str">
-        <v>Tolerance</v>
-      </c>
-      <c r="J26" t="str">
-        <v>1.0</v>
-      </c>
-      <c r="K26" t="str">
-        <v>Tolerance Operator</v>
-      </c>
-      <c r="L26" t="str">
-        <v>&lt;</v>
+      <c r="C25" t="str">
+        <v>10.2</v>
+      </c>
+      <c r="D25" t="str">
+        <v>10.1</v>
+      </c>
+      <c r="E25" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Location</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Front</v>
-      </c>
-      <c r="C27" t="str">
-        <v>Back</v>
-      </c>
-      <c r="D27" t="str">
-        <v>Left</v>
-      </c>
-      <c r="E27" t="str">
-        <v>Right</v>
-      </c>
-      <c r="F27" t="str">
-        <v>Max Leakage</v>
-      </c>
-      <c r="G27" t="str">
-        <v>Unit</v>
-      </c>
-      <c r="H27" t="str">
-        <v>Remark</v>
+        <v>TEST: RADIATION LEAKAGE LEVEL FROM X-RAY TUBE HOUSE</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Tube</v>
+        <v>kV</v>
       </c>
       <c r="B28" t="str">
-        <v>0.01</v>
+        <v>120</v>
       </c>
       <c r="C28" t="str">
-        <v>0.015</v>
+        <v>mA</v>
       </c>
       <c r="D28" t="str">
-        <v>0.012</v>
+        <v>10</v>
       </c>
       <c r="E28" t="str">
-        <v>0.011</v>
+        <v>Time</v>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>1.0</v>
       </c>
       <c r="G28" t="str">
-        <v>mGy/h</v>
+        <v>Workload</v>
       </c>
       <c r="H28" t="str">
-        <v/>
+        <v>100</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Tolerance</v>
+      </c>
+      <c r="J28" t="str">
+        <v>1.0</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Tolerance Operator</v>
+      </c>
+      <c r="L28" t="str">
+        <v>&lt;</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Collimator</v>
+        <v>Location</v>
       </c>
       <c r="B29" t="str">
+        <v>Front</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Back</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Left</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Right</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Max Leakage</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Remark</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Tube</v>
+      </c>
+      <c r="B30" t="str">
+        <v>0.01</v>
+      </c>
+      <c r="C30" t="str">
+        <v>0.015</v>
+      </c>
+      <c r="D30" t="str">
         <v>0.012</v>
       </c>
-      <c r="C29" t="str">
+      <c r="E30" t="str">
         <v>0.011</v>
       </c>
-      <c r="D29" t="str">
-        <v>0.014</v>
-      </c>
-      <c r="E29" t="str">
-        <v>0.013</v>
-      </c>
-      <c r="F29" t="str">
-        <v/>
-      </c>
-      <c r="G29" t="str">
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
         <v>mGy/h</v>
       </c>
-      <c r="H29" t="str">
+      <c r="H30" t="str">
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>TEST: RADIATION PROTECTION SURVEY REPORT</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>Applied Current (mA)</v>
-      </c>
-      <c r="B32" t="str">
-        <v>10</v>
-      </c>
-      <c r="C32" t="str">
-        <v>Applied Voltage (kV)</v>
-      </c>
-      <c r="D32" t="str">
-        <v>80</v>
-      </c>
-      <c r="E32" t="str">
-        <v>Exposure Time (s)</v>
-      </c>
-      <c r="F32" t="str">
-        <v>1.0</v>
-      </c>
-      <c r="G32" t="str">
-        <v>Workload (mA.min/week)</v>
-      </c>
-      <c r="H32" t="str">
-        <v>100</v>
+        <v>Collimator</v>
+      </c>
+      <c r="B31" t="str">
+        <v>0.012</v>
+      </c>
+      <c r="C31" t="str">
+        <v>0.011</v>
+      </c>
+      <c r="D31" t="str">
+        <v>0.014</v>
+      </c>
+      <c r="E31" t="str">
+        <v>0.013</v>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v>mGy/h</v>
+      </c>
+      <c r="H31" t="str">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>LOCATION</v>
-      </c>
-      <c r="B33" t="str">
-        <v>MAX. RADIATION LEVEL (MR/HR)</v>
-      </c>
-      <c r="C33" t="str">
-        <v>MR/WEEK</v>
-      </c>
-      <c r="D33" t="str">
-        <v>STATUS</v>
-      </c>
-      <c r="E33" t="str">
-        <v>RESULT</v>
+        <v>TEST: RADIATION PROTECTION SURVEY REPORT</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Control Console</v>
+        <v>Applied Current (mA)</v>
       </c>
       <c r="B34" t="str">
-        <v>0.05</v>
+        <v>10</v>
       </c>
       <c r="C34" t="str">
-        <v/>
+        <v>Applied Voltage (kV)</v>
       </c>
       <c r="D34" t="str">
-        <v/>
+        <v>80</v>
       </c>
       <c r="E34" t="str">
-        <v>Worker</v>
+        <v>Exposure Time (s)</v>
+      </c>
+      <c r="F34" t="str">
+        <v>1.0</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Workload (mA.min/week)</v>
+      </c>
+      <c r="H34" t="str">
+        <v>100</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
+        <v>LOCATION</v>
+      </c>
+      <c r="B35" t="str">
+        <v>MAX. RADIATION LEVEL (MR/HR)</v>
+      </c>
+      <c r="C35" t="str">
+        <v>MR/WEEK</v>
+      </c>
+      <c r="D35" t="str">
+        <v>STATUS</v>
+      </c>
+      <c r="E35" t="str">
+        <v>RESULT</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Control Console</v>
+      </c>
+      <c r="B36" t="str">
+        <v>0.05</v>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v>Worker</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
         <v>Waiting Area</v>
       </c>
-      <c r="B35" t="str">
+      <c r="B37" t="str">
         <v>0.02</v>
       </c>
-      <c r="C35" t="str">
-        <v/>
-      </c>
-      <c r="D35" t="str">
-        <v/>
-      </c>
-      <c r="E35" t="str">
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
         <v>Public</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L35"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L37"/>
   </ignoredErrors>
 </worksheet>
 </file>